--- a/Result/checksun_type/精簡型電腦.xlsx
+++ b/Result/checksun_type/精簡型電腦.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>13.86</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>622.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>310.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>310.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>254.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>351.48</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>351.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>33.59448541262719</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>622</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>622.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>13.45</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>13.64</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>13.89</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>13.89</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>278.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>197.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>197.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>197.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>596.58</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>596.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>3.250773089455862</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>278</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>13.49</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>13.66</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>13.91</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>13.91</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>124.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>169.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>169</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>181.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>600.88</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>600.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3.356343553983777</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>124</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>13.54</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>13.69</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>13.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>448.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>180</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>193.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>602.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>602.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>3.824787796601896</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>448</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>13.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>13.72</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>13.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>79.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>184.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>184.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>203.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>601.48</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>601.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-20.76733840958295</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>79</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>13.65</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>13.74</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>13.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>13.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>57.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>198.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>198.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>211.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>602.86</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>602.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-15.62154233236188</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>57</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>13.66</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>13.76</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>13.97</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>137.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>197.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>197.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>207.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>604.94</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>604.9400000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-5.355349995890293</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>137</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>13.64</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>13.77</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>13.97</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>179.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>193.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>193</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>214.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>606.7</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>606.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>0.9304729846366229</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>179</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>13.78</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>472.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>207.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>207.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>199.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>605.62</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>605.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>5.376988921652355</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>472</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>472.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>13.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>13.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>221.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>221.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>175.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>604.28</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>604.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-19.85573791552702</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>146</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>13.59</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>13.77</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>54.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>224.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>224.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>176.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>612.1</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>612.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-20.26478561451441</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>54</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>217717</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>149413</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>216732</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>221658</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>301588</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>199194</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>216632</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>357016</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>609988</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>600689</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>797538</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>321219</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>681031</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>98.22</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>102.1</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>108.53</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>108.53</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>56740.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>35188.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>35188</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>41927.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>67904.3</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>67904.3</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-6555.29517624835</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>56740</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>56740.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>96.91999999999999</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>102.27</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>109.01</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>102.27</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>109.01</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>25605.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>31832.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>31832.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>39182.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>74703.86</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>74703.86</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-8837.15468251572</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>25605</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>25605.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>96.55999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>102.64</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>109.64</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>109.64</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>20094.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>36278.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>36278.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>41102.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>80299.32</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>80299.32000000001</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-8445.448452807832</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>20094</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>20094.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>96.78</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>110.29</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>110.29</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>44443.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>48546.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>48546.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>42314.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>102251.34</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>102251.34</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-6993.780679910575</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>44443</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>44443.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>98.02000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>103.66</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>110.93</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>103.66</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>110.93</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>29058.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>44974.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>44974.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>49026.0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>113565.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>113565</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-7279.013122917677</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>29058</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>29058.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>99.06</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>104.09</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>111.3</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>111.3</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>39962.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>48666.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>48666.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>79835.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>116368.78</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>116368.78</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-5778.130429966477</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>39962</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>39962.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>100.26</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>104.69</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>111.67</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>104.69</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>111.67</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>47834.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>46533.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>46533.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>86486.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>117941.2</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>117941.2</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-4595.936210394531</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>47834</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>47834.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>101.02</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>105.16</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>105.16</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>112</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>81434.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>45926.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>45926.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>94455.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>120355.22</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>120355.22</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-3586.375317777667</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>81434</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>81434.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>101.7</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>105.52</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>112.22</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>105.52</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>112.22</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>26586.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>36082.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>36082.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>92477.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>122811.3</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>122811.3</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-5616.060638404379</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>26586</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>26586.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>101.9</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>105.82</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>112.49</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>105.82</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>112.49</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>47518.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>53077.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>53077.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>95272.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>127168.1</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>127168.1</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-2438.466073642354</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>47518</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>47518.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>102.4</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>112.78</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>106</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>112.78</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>29295.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>111004.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>111004.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>93714.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>133356.68</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>133356.68</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-54.67147849511821</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>29295</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>29295.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>3847834.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1895258.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1895258.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1471399.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2167598.64</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2167598.64</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>128725.1200794668</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>3847834</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>3847834.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1233198.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1369663.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1369663.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1363475.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2148522.86</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2148522.86</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-64816.37283714046</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1233198</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1233198.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>19.86</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1932137.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1292743.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1292743</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1286115.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2147117.6</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2147117.6</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-58849.77797382418</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1932137</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1932137.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>19.92</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1146463.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1259223.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1259223.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1347515.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2123313.92</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2123313.92</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-123110.6146700217</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1146463</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1146463.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>19.51</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1316660.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1103917.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1103917</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1374269.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2138601.12</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2138601.12</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-126335.6451406602</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1316660</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1316660.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>19.62</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1219860.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1047540.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1047540.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1310455.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2150367.64</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2150367.64</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-144666.2370579774</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1219860</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1219860.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>19.78</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>848595.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1357286.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1357286.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1330086.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2135168.2</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2135168.2</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-155314.7170449309</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>848595</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>848595.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>19.85</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>20.08</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>20.16</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>1764538.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1279488.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1279488.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1676457.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2144303.58</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2144303.58</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-125201.4842746884</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>1764538</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>1764538.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>369932.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1435808.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1435808.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1636380.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2147606.34</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2147606.34</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-175847.8487359602</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>369932</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>369932.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1034779.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1644622.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1644622</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1680797.2</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2162187.9</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2162187.9</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-92497.44622577867</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1034779</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1034779.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>2768590.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1573370.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1573370.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1650880.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2155087.0</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2155087</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-41355.5695603129</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>2768590</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>2768590.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>52.66</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>59.14</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>61.98</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>59.14</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>61.98</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>19370245.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>16724922.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>16724922.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>29736079.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>59920226.2</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>59920226.2</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-7654864.406155422</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>19370245</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>19370245.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>52.4</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>59.83</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>62.09</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>62.09</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>11627684.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>17947425.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>17947425.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>29554414.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>59980908.68</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>59980908.68</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-8179897.695759896</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>11627684</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>11627684.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>52.22000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>60.59</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>62.24</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>62.24</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>8231015.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>24035589.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>24035589.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>33395445.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>60054884.02</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>60054884.02</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-7808245.941774867</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>8231015</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>8231015.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>52.56</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>61.45</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>62.4</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>20875162.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>41337116.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>41337116.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>34879692.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>60292638.06</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>60292638.06</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-6634520.116732866</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>20875162</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>20875162.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>53.9</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>62.33</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>62.58</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>62.58</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>23520508.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>43669028.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>43669028.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>35113728.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>60099849.48</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>60099849.48</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-6075551.826789543</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>23520508</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>23520508.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>55.48</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>63.26</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>62.74</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>62.74</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>25482760.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>42747237.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>42747237</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>35341328.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>59951906.28</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>59951906.28</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-5343471.633056603</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>25482760</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>25482760.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>64.16</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>62.9</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>62.9</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>42068504.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>41161403.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>41161403</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>36260327.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>59925738.76</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>59925738.76</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-4317045.797971807</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>42068504</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>42068504.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>58.94000000000001</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>65.18</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>63.1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>94738649.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>42755300.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>42755300.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>40238517.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>59413146.08</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>59413146.08</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-4473586.969351687</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>94738649</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>94738649.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>60.72000000000001</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>63.25</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>63.25</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>32534721.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>28422268.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>28422268.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>43417093.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>58054167.8</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>58054167.8</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-10180676.07241751</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>32534721</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>32534721.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>61.34</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>67.29</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>63.35</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>63.35</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>18911551.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>26558429.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>26558429.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>42703332.8</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>58228467.96</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>58228467.96</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-11305358.35992521</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>18911551</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>18911551.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>61.82000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>67.95</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>63.45</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>63.45</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>17553590.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>27935419.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>27935419.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>45075687.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>58337032.66</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>58337032.66</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-11048659.18636745</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>17553590</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>17553590.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>23.56</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>24.26</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>683368.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1065936.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1065936</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1204760.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1007853.06</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1007853.06</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-44728.03969816875</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>683368</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>683368.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>23.56</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>24.08</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>24.27</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>24.27</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>238873.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1028308.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1028308.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1190971.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1018334.22</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1018334.22</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-12499.46051219967</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>238873</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>238873.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>23.61</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>24.13</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>24.28</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>24.28</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1261260.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1548817.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1548817</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1361207.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1082554.34</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1082554.34</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>81612.2404860491</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1261260</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1261260.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>23.75</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>24.19</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>24.3</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>2111747.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1563660.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1563660.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1305082.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1087680.1</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1087680.1</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>103601.3404661885</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>2111747</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>2111747.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>23.85</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>24.23</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>24.33</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>24.33</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1034432.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1313185.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1313185.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1195387.5</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1060501.36</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1060501.36</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>40190.68542116648</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1034432</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1034432.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>23.96</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>24.27</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>24.35</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>495232.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1343585.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1343585.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1174492.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1053422.64</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1053422.64</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>63595.26087752194</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>495232</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>495232.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>24.05</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>24.37</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>24.37</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2841414.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1353634.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1353634.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1197907.4</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1057437.04</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1057437.04</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>152530.5379266902</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2841414</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2841414.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>24.11</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>24.39</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>24.39</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1335476.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1173597.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1173597</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1064613.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1033129.1</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1033129.1</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>22756.77164240554</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1335476</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1335476.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>24.14</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>24.37</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>24.41</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>859373.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1046504.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1046504.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1021377.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>1049371.7</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>1049371.7</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-2096.564893801347</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>859373</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>859373.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>24.22</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>24.39</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>24.44</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1186431.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1077589.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1077589.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1095247.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>1167872.3</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>1167872.3</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>13484.58165782481</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1186431</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1186431.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>24.27</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>24.44</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>545479.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1005400.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1005400.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1021076.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1202076.34</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1202076.34</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>219.8416723683476</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>545479</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>545479.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>15.4</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>17.06</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>5652361.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>5028740.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>5028740.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>5082372.1</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>9353209.66</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>9353209.66</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-550819.24096628</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>5652361</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>5652361.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,21 +29867,17 @@
           <t>15.19</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AM69" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AO69" t="inlineStr">
         <is>
           <t>17.08</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
       <c r="AP69" t="inlineStr">
         <is>
           <t>-5.73</t>
@@ -30324,20 +29918,16 @@
           <t>4424717.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>5329736.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>5329736.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>5103575.5</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>9555470.46</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>9555470.460000001</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-648683.641199653</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>4424717</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>4424717.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>15.08</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>16.22</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>17.11</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>4327685.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>5531374.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>5531374</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>5269643.4</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>9641382.96</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>9641382.960000001</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-633789.3686330551</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>4327685</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>4327685.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>15.15</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>17.16</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>17.16</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>6690412.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5300118.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>5300118.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>5787760.5</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>9843256.0</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>9843256</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-579480.2160867341</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>6690412</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>6690412.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>15.34</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>16.49</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>17.22</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>17.22</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>4048526.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4772087.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4772087.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>6359425.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>9834106.22</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>9834106.220000001</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-734349.3118746076</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>4048526</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>4048526.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>15.46</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>17.27</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>17.27</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>7157344.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>5136004.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>5136004</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>6642532.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>10066994.44</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>10066994.44</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-646304.9018617617</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>7157344</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>7157344.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>15.71</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>16.73</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>17.34</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>5432903.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>4877414.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>4877414.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>7124230.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>10221143.24</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>10221143.24</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-830532.4982054904</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>5432903</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>5432903.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>15.8</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>16.84</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>17.4</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>3171406.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>5007912.8</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>5007912.8</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>7319766.2</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>10347646.84</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>10347646.84</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-879291.368046335</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>3171406</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>3171406.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>15.82</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>17.46</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>17.46</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>4050259.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>6275402.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>6275402.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>7969517.0</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>10765668.22</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>10765668.22</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-675240.3832458872</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>4050259</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>4050259.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>15.89</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>17.52</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>17.52</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>5868108.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>7946762.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>7946762.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>8174205.8</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>11304182.02</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>11304182.02</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-453786.0698436089</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>5868108</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>5868108.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,21 +33737,17 @@
           <t>16.0</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AM78" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="AO78" t="inlineStr">
         <is>
           <t>17.08</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
       <c r="AP78" t="inlineStr">
         <is>
           <t>-66.18</t>
@@ -34248,20 +33788,16 @@
           <t>5864395.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>8149061.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>8149061.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>8528054.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>11829181.46</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>11829181.46</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-315985.65534594</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>5864395</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>5864395.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>243.9</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>262.3</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>276.85</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>262.3</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>276.85</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>733798218.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1194062426.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1194062426</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1580682611.2</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1719388067.76</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1719388067.76</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-66910632.68277311</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>733798218</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>733798218.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>242.6</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>264.23</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>277.41</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>264.23</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>277.41</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>850292929.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1423462573.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1423462573.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1600931496.7</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>1724439125.3</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>1724439125.3</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-14236824.32551908</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>850292929</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>850292929.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>243.3</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>266.42</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>278.1</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>266.42</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>278.1</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>1357346993.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1837049872.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1837049872</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1584059781.4</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>1770696953.38</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>1770696953.38</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>49038355.16075516</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1357346993</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1357346993.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>245.8</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>268.5</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>278.92</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>278.92</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1304530306.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>2208769721.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>2208769721.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1552615207.7</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>1804193227.82</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>1804193227.82</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>83352877.74254823</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1304530306</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1304530306.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>252.0</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>270.5</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>279.62</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>279.62</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1724343684.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>2198178141.6</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>2198178141.6</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1512921772.9</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1791378007.68</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1791378007.68</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>135055666.5471616</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1724343684</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1724343684.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>256.4</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>272.2</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>280.04</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>280.04</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>1880798955.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1967302796.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1967302796.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1540485367.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1765544380.32</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1765544380.32</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>159113371.9627824</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1880798955</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1880798955.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>262.7</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>274.62</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>280.55</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>274.62</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>280.55</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>2918229422.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1778400420.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1778400420</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1443108304.0</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1736673951.92</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1736673951.92</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>171035837.3792841</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>2918229422</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>2918229422.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>268.5</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>276.58</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>280.91</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>276.58</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>280.91</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>3215946240.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1331069690.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1331069690.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1319551651.8</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>1685350788.7</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>1685350788.7</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>70806243.74645543</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>3215946240</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>3215946240.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>272.5</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>277.7</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>281.06</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>277.7</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>281.06</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>1251572407.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>896460694.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>896460694</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1086040261.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>1638145283.6</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>1638145283.6</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-106805914.934245</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1251572407</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1251572407.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>272.6</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>278.32</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>280.98</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>278.32</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>280.98</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>569966958.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>827665404.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>827665404.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1063949427.6</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>1639177449.86</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>1639177449.86</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-146254448.2661656</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>569966958</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>569966958.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>274.3</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>278.77</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>281.12</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>278.77</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>281.12</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>936287073.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1113667938.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1113667938.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1099219795.8</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>1643378817.02</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>1643378817.02</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-124356967.480832</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>936287073</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>936287073.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>68.38</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>69.24</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>72.34</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>72.34</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>20830667.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>32787545.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>32787545.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>65620149.1</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>23425086.84</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>23425086.84</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>220651.9558153227</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>20830667</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>20830667.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>68.64</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>72.6</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>15528014.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>36125377.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>36125377.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>64155332.6</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>24303418.6</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>24303418.6</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>2542064.812653594</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>15528014</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>15528014.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>69.41999999999999</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>72.92</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>39991170.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>45273325.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>45273325</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>63567588.0</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>25594879.48</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>25594879.48</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>6335722.257684931</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>39991170</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>39991170.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>71.41999999999999</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>69.65</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>73.3</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>65712989.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>90535539.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>90535539</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>60180901.0</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>27453216.76</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>27453216.76</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>8907904.669955224</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>65712989</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>65712989.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>72.84</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>69.72</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>73.52</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>73.52</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>21874887.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>100758207.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>100758207.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>54278327.5</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>27897210.66</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>27897210.66</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>9508402.34212868</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>21874887</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>21874887.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>72.66</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>69.75</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>73.66</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>73.66</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>37519829.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>98452752.8</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>98452752.8</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>52876974.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>28032130.42</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>28032130.42</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>14723609.86158616</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>37519829</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>37519829.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>72.24</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>69.79</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>73.77</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>73.77</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>61267750.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>92185287.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>92185287.40000001</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>50408301.4</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>28359429.14</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>28359429.14</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>19971819.32289735</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>61267750</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>61267750.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>70.97999999999999</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>69.68</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>73.81</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>73.81</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>266302240.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>81861851.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>81861851</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>45243343.6</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>27556699.06</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>27556699.06</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>24211562.04180986</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>266302240</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>266302240.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>68.9</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>69.38</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>73.73</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>69.38</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>73.73</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>116826331.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>29826263.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>29826263</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>19040700.4</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>22921909.88</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>22921909.88</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>7435657.638763092</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>116826331</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>116826331.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>67.16</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>69.17</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>73.7</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>69.17</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>73.7</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>10347614.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>7798447.6</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>7798447.6</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>7992288.4</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>21742097.52</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>21742097.52</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-780203.3169738334</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>10347614</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>10347614.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>66.96000000000001</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>73.87</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>73.87</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>6182502.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>7301195.2</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>7301195.2</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>7833449.9</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>22504769.96</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>22504769.96</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-1080849.170991799</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>6182502</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>6182502.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>2251806679</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>2303990317</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>4282414081</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>3277325446</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>2111926901</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>2504000596</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>6330911536</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>3971577357</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>2253776059</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>3252501668</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>3950855603</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>10702402903</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>9579043601</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>16911194399</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>15812987742</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>15882778006</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>10973548400</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>12353712685</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>10709769939</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>18182742782</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>10733728288</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>13958553198</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
